--- a/evol-wording/ig/StructureDefinition-xdmDocumentEntry.xlsx
+++ b/evol-wording/ig/StructureDefinition-xdmDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T10:08:13+00:00</t>
+    <t>2026-08-07T10:10:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/evol-wording/ig/StructureDefinition-xdmDocumentEntry.xlsx
+++ b/evol-wording/ig/StructureDefinition-xdmDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T10:10:33+00:00</t>
+    <t>2026-08-12T09:48:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
